--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487757_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487757_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4256</v>
+        <v>7.5525</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2933</v>
+        <v>8.0931</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8677</v>
+        <v>-0.5406</v>
       </c>
       <c r="G2" t="n">
         <v>0.0386</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5323</v>
+        <v>-0.4055</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4218</v>
+        <v>-0.622</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1106</v>
+        <v>0.2165</v>
       </c>
       <c r="V2" t="n">
         <v>6.5611</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAWARA</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0487</v>
+        <v>0.6483</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6814</v>
+        <v>1.0447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3673</v>
+        <v>-0.3964</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1051</v>
+        <v>0.4124</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6708</v>
+        <v>-0.3823</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4344</v>
+        <v>0.7947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07240000000000001</v>
+        <v>1.3809</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0494</v>
+        <v>0.0412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1218</v>
+        <v>1.3397</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1775</v>
+        <v>-0.9685</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6214</v>
+        <v>-0.4235</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5561</v>
+        <v>-0.545</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7463</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4076</v>
+        <v>-0.0939</v>
       </c>
       <c r="T3" t="n">
-        <v>0.609</v>
+        <v>-0.1422</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7986</v>
+        <v>0.0482</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4923</v>
+        <v>0.3016</v>
       </c>
       <c r="E4" t="n">
         <v>0.1456</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3467</v>
+        <v>0.1559</v>
       </c>
       <c r="G4" t="n">
         <v>0.0498</v>
@@ -766,13 +766,13 @@
         <v>0.7761</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3336</v>
+        <v>-0.5243</v>
       </c>
       <c r="T4" t="n">
         <v>-0.5451</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2115</v>
+        <v>0.0208</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>M. DIAWARA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4392</v>
+        <v>-0.1247</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9446</v>
+        <v>-0.2195</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5054</v>
+        <v>0.0948</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4124</v>
+        <v>-2.1051</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3823</v>
+        <v>-1.6708</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7947</v>
+        <v>-0.4344</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3809</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0412</v>
+        <v>-0.0494</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3397</v>
+        <v>0.1218</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9685</v>
+        <v>-2.1775</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4235</v>
+        <v>-1.6214</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.545</v>
+        <v>-0.5561</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.7463</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3031</v>
+        <v>0.2341</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2423</v>
+        <v>-0.2919</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0608</v>
+        <v>0.526</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4318</v>
+        <v>-0.4045</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7073</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2755</v>
+        <v>0.3028</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7192</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0424</v>
+        <v>-0.0151</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V6" t="n">
         <v>0.3299</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5945</v>
+        <v>-1.5405</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4106</v>
+        <v>-0.7109</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1839</v>
+        <v>-0.8296</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5772</v>
@@ -1000,13 +1000,13 @@
         <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5994</v>
+        <v>-0.5454</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3017</v>
+        <v>-0.602</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2977</v>
+        <v>0.0567</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0234</v>
+        <v>-1.904</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4029</v>
+        <v>-0.6021</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-1.3019</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3546</v>
@@ -1078,13 +1078,13 @@
         <v>2.1344</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3107</v>
+        <v>-0.1912</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.817</v>
+        <v>-1.0162</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5063</v>
+        <v>0.825</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2985</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.409</v>
+        <v>-2.0725</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1061</v>
+        <v>-0.9059</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3029</v>
+        <v>-1.1666</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4783</v>
@@ -1156,13 +1156,13 @@
         <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0487</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2113</v>
+        <v>-1.0111</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1626</v>
+        <v>0.2989</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0164</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.464</v>
+        <v>-2.1364</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0715</v>
+        <v>-2.7712</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6075</v>
+        <v>0.6348</v>
       </c>
       <c r="G10" t="n">
         <v>-1.312</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3699</v>
+        <v>-0.0423</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7268</v>
+        <v>-0.4265</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3569</v>
+        <v>0.3842</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7821</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ SANCHEZ</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5428</v>
+        <v>-2.37</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1414</v>
+        <v>-1.4343</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4014</v>
+        <v>-0.9358</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7344</v>
+        <v>-0.6617</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7423</v>
+        <v>0.5734</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9921</v>
+        <v>-1.2351</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9002</v>
+        <v>0.8633</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.7415</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2535</v>
+        <v>0.1218</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1658</v>
+        <v>-1.525</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0956</v>
+        <v>-0.1681</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2614</v>
+        <v>-1.3569</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5821</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.0544</v>
       </c>
       <c r="T11" t="n">
-        <v>0.729</v>
+        <v>-0.1632</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0612</v>
+        <v>0.2176</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.894</v>
+        <v>-0.4045</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.894</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>S. KIMOTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6793</v>
+        <v>-2.954</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6345</v>
+        <v>-2.6039</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0448</v>
+        <v>-0.3501</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6617</v>
+        <v>-2.7451</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5734</v>
+        <v>-1.9443</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2351</v>
+        <v>-0.8008</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8633</v>
+        <v>-2.2986</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7415</v>
+        <v>-0.9639</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1218</v>
+        <v>-1.3347</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.525</v>
+        <v>-0.4466</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1681</v>
+        <v>-0.9804</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3569</v>
+        <v>0.5339</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2548</v>
+        <v>-0.4029</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3634</v>
+        <v>-0.3054</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1086</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4045</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. KIMOTO</t>
+          <t>A. FERNANDEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2543</v>
+        <v>-2.9887</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9042</v>
+        <v>-2.6419</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3501</v>
+        <v>-0.3469</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7451</v>
+        <v>-1.7344</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9443</v>
+        <v>-0.7423</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8008</v>
+        <v>-0.9921</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2986</v>
+        <v>-1.9002</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9639</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3347</v>
+        <v>-1.2535</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4466</v>
+        <v>0.1658</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9804</v>
+        <v>-0.0956</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5339</v>
+        <v>0.2614</v>
       </c>
       <c r="P13" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R13" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7032</v>
+        <v>0.2218</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6057</v>
+        <v>0.2285</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0067</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.993300000000001</v>
+        <v>-7.992899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.313600000000001</v>
+        <v>-3.313599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.6797</v>
+        <v>-4.6796</v>
       </c>
       <c r="G14" t="n">
         <v>-15.1868</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.816599999999999</v>
+        <v>-5.8166</v>
       </c>
       <c r="I14" t="n">
         <v>-9.3705</v>
@@ -1546,13 +1546,13 @@
         <v>13.5823</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4227</v>
+        <v>-2.4225</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.9577</v>
+        <v>-4.957699999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5348</v>
+        <v>2.535</v>
       </c>
       <c r="V14" t="n">
         <v>2.825400000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0377</v>
+        <v>3.9014</v>
       </c>
       <c r="E15" t="n">
         <v>2.7401</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2975</v>
+        <v>1.1613</v>
       </c>
       <c r="G15" t="n">
         <v>3.8735</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7941</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3623</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1564</v>
+        <v>1.0201</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0478</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4664</v>
+        <v>3.3001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3861</v>
+        <v>3.177</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0803</v>
+        <v>0.1231</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7993</v>
+        <v>3.3644</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3989</v>
+        <v>-0.0568</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4004</v>
+        <v>3.4213</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0216</v>
+        <v>2.995</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6889</v>
+        <v>0.6303</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6673</v>
+        <v>2.3647</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.3695</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.29</v>
+        <v>-0.6871</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0677</v>
+        <v>1.0566</v>
       </c>
       <c r="P16" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R16" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4731</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3645</v>
+        <v>-0.4896</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1086</v>
+        <v>0.3954</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3452</v>
+        <v>2.2752</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5764</v>
+        <v>1.0858</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2312</v>
+        <v>1.1893</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3644</v>
+        <v>1.7993</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0568</v>
+        <v>1.3989</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4213</v>
+        <v>0.4004</v>
       </c>
       <c r="J17" t="n">
-        <v>2.995</v>
+        <v>1.0216</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6303</v>
+        <v>1.6889</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3647</v>
+        <v>-0.6673</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3695</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6871</v>
+        <v>-0.29</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0566</v>
+        <v>1.0677</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0491</v>
+        <v>0.2818</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0902</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0411</v>
+        <v>0.2176</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9741</v>
+        <v>1.5018</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8241000000000001</v>
+        <v>1.3246</v>
       </c>
       <c r="F18" t="n">
-        <v>0.15</v>
+        <v>0.1773</v>
       </c>
       <c r="G18" t="n">
         <v>3.8419</v>
@@ -1858,13 +1858,13 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6738</v>
+        <v>-0.1461</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9691</v>
+        <v>-0.4686</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2952</v>
+        <v>0.3225</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7907999999999999</v>
+        <v>1.3552</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3911</v>
+        <v>2.0918</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.7366</v>
       </c>
       <c r="G19" t="n">
         <v>1.6485</v>
@@ -1936,13 +1936,13 @@
         <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.48</v>
+        <v>0.0844</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2719</v>
+        <v>-0.5712</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7919</v>
+        <v>0.6556</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3776</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3367</v>
+        <v>0.2009</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9332</v>
+        <v>-2.6329</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2699</v>
+        <v>2.8338</v>
       </c>
       <c r="G20" t="n">
         <v>1.0365</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5808</v>
+        <v>0.445</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1508</v>
+        <v>-0.8505</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7315</v>
+        <v>1.2955</v>
       </c>
       <c r="V20" t="n">
         <v>0.6597</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BUTUNOI</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.1405</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.04</v>
+        <v>-0.8542</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0543</v>
+        <v>0.9947</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0519</v>
+        <v>0.362</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1854</v>
+        <v>0.739</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1335</v>
+        <v>-0.377</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0206</v>
+        <v>0.5029</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0206</v>
+        <v>1.1246</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.6217</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0725</v>
+        <v>-0.1409</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.206</v>
+        <v>-0.3856</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1335</v>
+        <v>0.2447</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0424</v>
+        <v>0.3606</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0606</v>
+        <v>-0.387</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0182</v>
+        <v>0.7476</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="E22" t="n">
         <v>-0.04</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0543</v>
+        <v>-0.0271</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0519</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0424</v>
+        <v>-0.0151</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>D. BUTUNOI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2464</v>
+        <v>-0.067</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2088</v>
+        <v>-0.04</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0376</v>
+        <v>-0.0271</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3258</v>
+        <v>-0.0519</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3699</v>
+        <v>-0.1854</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6957</v>
+        <v>0.1335</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.492</v>
+        <v>0.0206</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0536</v>
+        <v>0.0206</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5455</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1662</v>
+        <v>-0.0725</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3164</v>
+        <v>-0.206</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1502</v>
+        <v>0.1335</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4675</v>
+        <v>-0.0151</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9713000000000001</v>
+        <v>-0.0606</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5038</v>
+        <v>0.0454</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5052</v>
+        <v>-0.7018</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2546</v>
+        <v>-0.9095</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7494</v>
+        <v>0.2077</v>
       </c>
       <c r="G24" t="n">
-        <v>0.362</v>
+        <v>-0.3258</v>
       </c>
       <c r="H24" t="n">
-        <v>0.739</v>
+        <v>0.3699</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.377</v>
+        <v>-0.6957</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5029</v>
+        <v>-0.492</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1246</v>
+        <v>0.0536</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6217</v>
+        <v>-0.5455</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1409</v>
+        <v>0.1662</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3856</v>
+        <v>0.3164</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2447</v>
+        <v>-0.1502</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2851</v>
+        <v>0.0121</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7874</v>
+        <v>0.2706</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5023</v>
+        <v>-0.2585</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0174</v>
+        <v>-3.846</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0915</v>
+        <v>-1.593</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9259</v>
+        <v>-2.253</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3095</v>
@@ -2404,13 +2404,13 @@
         <v>0.9702</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6801</v>
+        <v>0.8516</v>
       </c>
       <c r="T25" t="n">
-        <v>1.882</v>
+        <v>0.3805</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7982</v>
+        <v>0.4711</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4477</v>
@@ -2443,16 +2443,16 @@
         <v>4.3497</v>
       </c>
       <c r="F26" t="n">
-        <v>3.643499999999999</v>
+        <v>3.6434</v>
       </c>
       <c r="G26" t="n">
         <v>15.187</v>
       </c>
       <c r="H26" t="n">
-        <v>5.8164</v>
+        <v>5.816400000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>9.370599999999998</v>
+        <v>9.370600000000001</v>
       </c>
       <c r="J26" t="n">
         <v>17.5984</v>
@@ -2461,7 +2461,7 @@
         <v>10.0349</v>
       </c>
       <c r="L26" t="n">
-        <v>7.563600000000001</v>
+        <v>7.5636</v>
       </c>
       <c r="M26" t="n">
         <v>-2.4112</v>
@@ -2470,7 +2470,7 @@
         <v>-4.218400000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>1.807</v>
+        <v>1.807000000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-6.791199999999999</v>
@@ -2488,7 +2488,7 @@
         <v>-2.5351</v>
       </c>
       <c r="U26" t="n">
-        <v>4.957800000000001</v>
+        <v>4.9577</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8254</v>
